--- a/templates/CAMPAIGN_TEMPLATE.xlsx
+++ b/templates/CAMPAIGN_TEMPLATE.xlsx
@@ -6344,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W200"/>
+  <dimension ref="A1:X200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="25" min="1" max="1"/>
@@ -6486,6 +6486,11 @@
       <c r="W1" s="39" t="inlineStr">
         <is>
           <t>notes</t>
+        </is>
+      </c>
+      <c r="X1" s="39" t="inlineStr">
+        <is>
+          <t>pipeline_step</t>
         </is>
       </c>
     </row>

--- a/templates/CAMPAIGN_TEMPLATE.xlsx
+++ b/templates/CAMPAIGN_TEMPLATE.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>01_Tobi_Posts</t>
+          <t>01_Bai_Mau</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Duc Nguyen</t>
+          <t>Tên người phụ trách</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Awareness — xây dựng Học cùng Tobi thành nguồn chia sẻ AI Agent dễ hiểu, thực tế và đáng tin cậy cho người làm Data.</t>
+          <t>Awareness — xây dựng Kênh mẫu thành nguồn chia sẻ AI Agent dễ hiểu, thực tế và đáng tin cậy cho người làm Data.</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -6497,7 +6497,7 @@
     <row r="2" ht="38.25" customHeight="1">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>TOBI-001</t>
+          <t>MAU-001</t>
         </is>
       </c>
       <c r="B2" s="30" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="V2" s="30" t="inlineStr">
         <is>
-          <t>assets/TOBI-001_ai-agent-la-gi</t>
+          <t>assets/MAU-001_ai-agent-la-gi</t>
         </is>
       </c>
       <c r="W2" s="30" t="n"/>
@@ -6554,7 +6554,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
-          <t>TOBI-002</t>
+          <t>MAU-002</t>
         </is>
       </c>
       <c r="B3" s="30" t="inlineStr">
@@ -6599,7 +6599,7 @@
       <c r="U3" s="31" t="n"/>
       <c r="V3" s="30" t="inlineStr">
         <is>
-          <t>assets/TOBI-002</t>
+          <t>assets/MAU-002</t>
         </is>
       </c>
       <c r="W3" s="30" t="n"/>
